--- a/WEEKLY REPORTING TEMPLATE.xlsx
+++ b/WEEKLY REPORTING TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A4AD8C-8E3A-2449-932F-FF1B07D18E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9E9C10-50A8-1845-A49E-E7904359B146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="760" windowWidth="27800" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="760" windowWidth="27800" windowHeight="17480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weekly Info" sheetId="10" r:id="rId1"/>
@@ -43,40 +43,6 @@
     <author>David Cuvin</author>
   </authors>
   <commentList>
-    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{D1652067-3673-6245-AC97-60B3C5FA5074}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>David Cuvin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Had to manually tally certain items from several invoices
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="A19" authorId="0" shapeId="0" xr:uid="{DF7890CD-0BEE-494A-A9E8-17B330A2D8AA}">
       <text>
         <r>
@@ -121,7 +87,7 @@
     <author>David Cuvin</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{EB595F93-B3E2-1F45-A1C0-5B130F428130}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{0AD7D3D6-088B-D64C-8908-1320951E84C9}">
       <text>
         <r>
           <rPr>
@@ -1357,10 +1323,7 @@
       <c r="A18" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="49">
-        <f>Invoices!G2</f>
-        <v>0</v>
-      </c>
+      <c r="B18" s="49"/>
       <c r="C18" s="49"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
@@ -1587,7 +1550,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="16">
-        <f>SUM(Event_PnL!B11:'Event_PnL'!Z11)</f>
+        <f>SUM(Event_PnL!B11:Z11)</f>
         <v>0</v>
       </c>
     </row>
@@ -1605,7 +1568,7 @@
         <v>45</v>
       </c>
       <c r="B4" s="18">
-        <f>SUM((Event_PnL!B18:'Event_PnL'!Z18):(Event_PnL!B19:'Event_PnL'!Z19))</f>
+        <f>SUM((Event_PnL!B18:Z18):(Event_PnL!B19:Z19))</f>
         <v>0</v>
       </c>
     </row>
@@ -1622,9 +1585,9 @@
       <c r="A6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="18" t="e">
-        <f>SUM(Event_PnL!#REF!:Event_PnL!#REF!)</f>
-        <v>#REF!</v>
+      <c r="B6" s="18">
+        <f>SUM(Event_PnL!B17:Z17)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1633,7 +1596,7 @@
       </c>
       <c r="B7" s="19" t="e">
         <f>B6/B3</f>
-        <v>#REF!</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1641,7 +1604,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="18">
-        <f>SUM(Event_PnL!B10:'Event_PnL'!Z10)</f>
+        <f>SUM(Event_PnL!B10:Z10)</f>
         <v>0</v>
       </c>
     </row>
@@ -1649,9 +1612,9 @@
       <c r="A9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="18" t="e">
+      <c r="B9" s="18">
         <f>SUM(B4,B6)</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1659,7 +1622,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="18">
-        <f>SUM(Event_PnL!B23:'Event_PnL'!Z23)</f>
+        <f>SUM(Event_PnL!B23:Z23)</f>
         <v>0</v>
       </c>
     </row>
@@ -1669,7 +1632,7 @@
       </c>
       <c r="B11" s="19" t="e">
         <f>B9/B3</f>
-        <v>#REF!</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">

--- a/WEEKLY REPORTING TEMPLATE.xlsx
+++ b/WEEKLY REPORTING TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9E9C10-50A8-1845-A49E-E7904359B146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E87ACF0-C0F4-CA4D-8C9C-24294E6964D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="760" windowWidth="27800" windowHeight="17480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2440" yWindow="1200" windowWidth="27800" windowHeight="17480" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weekly Info" sheetId="10" r:id="rId1"/>
@@ -43,6 +43,174 @@
     <author>David Cuvin</author>
   </authors>
   <commentList>
+    <comment ref="A14" authorId="0" shapeId="0" xr:uid="{B0519644-9158-EC41-AED3-19330A6EADCB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>David Cuvin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>day-of-event</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="0" shapeId="0" xr:uid="{CE3EC192-6BFF-E94C-B8F6-A4B89078C45E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>David Cuvin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>day-of-event</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0" xr:uid="{2EFA2898-612E-294D-9F1A-1CBBB58105C9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>David Cuvin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>day-of-event</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0" xr:uid="{DDB944F3-551D-CD42-BE33-334D9A2F1ECC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>David Cuvin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>day-of-event</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="A19" authorId="0" shapeId="0" xr:uid="{DF7890CD-0BEE-494A-A9E8-17B330A2D8AA}">
       <text>
         <r>
@@ -164,7 +332,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{1674F2E2-DE8B-E346-96FA-B78AED0AF249}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{D2C6418D-A11A-774B-8EE3-81F8DBA95B0E}">
       <text>
         <r>
           <rPr>
@@ -193,7 +361,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>total weekly labor required (prep, set-up, etc.)</t>
+          <t xml:space="preserve">total weekly labor required (prep, set-up, etc.) + 15% Buffer
+</t>
         </r>
       </text>
     </comment>
@@ -364,7 +533,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,8 +626,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,6 +656,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -561,7 +743,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -726,6 +908,9 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1586,7 +1771,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="18">
-        <f>SUM(Event_PnL!B17:Z17)</f>
+        <f>SUM(Labor!D2)</f>
         <v>0</v>
       </c>
     </row>
@@ -1657,9 +1842,9 @@
   <cols>
     <col min="1" max="1" width="21" style="7" customWidth="1"/>
     <col min="2" max="2" width="53.1640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="15" style="10" customWidth="1"/>
-    <col min="4" max="4" width="7.1640625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="26" style="11" customWidth="1"/>
+    <col min="5" max="5" width="28.1640625" style="7" customWidth="1"/>
     <col min="6" max="16384" width="8.83203125" style="7"/>
   </cols>
   <sheetData>
@@ -1673,17 +1858,14 @@
       <c r="C1" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="D1" s="25" t="s">
         <v>24</v>
       </c>
+      <c r="E1" s="63"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="9"/>
-      <c r="E2" s="11">
-        <f>SUM(C2:C100)</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="8"/>
